--- a/artfynd/A 26160-2024 artfynd.xlsx
+++ b/artfynd/A 26160-2024 artfynd.xlsx
@@ -3378,12 +3378,7 @@
         <v>69943578</v>
       </c>
       <c r="B24" t="n">
-        <v>101976</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>104325</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3426,10 +3421,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>600912.9165476782</v>
+        <v>600913</v>
       </c>
       <c r="R24" t="n">
-        <v>6292237.519167135</v>
+        <v>6292238</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -3464,19 +3459,9 @@
           <t>2011-07-10</t>
         </is>
       </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2011-07-10</t>
-        </is>
-      </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3501,7 +3486,7 @@
       </c>
       <c r="AY24" t="inlineStr">
         <is>
-          <t>Floraväkteri Sverige</t>
+          <t>Inventering av Ölands kärlväxtflora., Floraväkteri Sverige</t>
         </is>
       </c>
     </row>

--- a/artfynd/A 26160-2024 artfynd.xlsx
+++ b/artfynd/A 26160-2024 artfynd.xlsx
@@ -3378,7 +3378,7 @@
         <v>69943578</v>
       </c>
       <c r="B24" t="n">
-        <v>104325</v>
+        <v>104334</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>

--- a/artfynd/A 26160-2024 artfynd.xlsx
+++ b/artfynd/A 26160-2024 artfynd.xlsx
@@ -3378,7 +3378,7 @@
         <v>69943578</v>
       </c>
       <c r="B24" t="n">
-        <v>104334</v>
+        <v>104346</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>

--- a/artfynd/A 26160-2024 artfynd.xlsx
+++ b/artfynd/A 26160-2024 artfynd.xlsx
@@ -3378,7 +3378,7 @@
         <v>69943578</v>
       </c>
       <c r="B24" t="n">
-        <v>104346</v>
+        <v>104355</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>

--- a/artfynd/A 26160-2024 artfynd.xlsx
+++ b/artfynd/A 26160-2024 artfynd.xlsx
@@ -3378,7 +3378,7 @@
         <v>69943578</v>
       </c>
       <c r="B24" t="n">
-        <v>104355</v>
+        <v>104358</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>

--- a/artfynd/A 26160-2024 artfynd.xlsx
+++ b/artfynd/A 26160-2024 artfynd.xlsx
@@ -3378,7 +3378,7 @@
         <v>69943578</v>
       </c>
       <c r="B24" t="n">
-        <v>104358</v>
+        <v>104385</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>

--- a/artfynd/A 26160-2024 artfynd.xlsx
+++ b/artfynd/A 26160-2024 artfynd.xlsx
@@ -3378,7 +3378,7 @@
         <v>69943578</v>
       </c>
       <c r="B24" t="n">
-        <v>104385</v>
+        <v>104391</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>

--- a/artfynd/A 26160-2024 artfynd.xlsx
+++ b/artfynd/A 26160-2024 artfynd.xlsx
@@ -3378,7 +3378,7 @@
         <v>69943578</v>
       </c>
       <c r="B24" t="n">
-        <v>104412</v>
+        <v>104417</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>

--- a/artfynd/A 26160-2024 artfynd.xlsx
+++ b/artfynd/A 26160-2024 artfynd.xlsx
@@ -3378,7 +3378,7 @@
         <v>69943578</v>
       </c>
       <c r="B24" t="n">
-        <v>104417</v>
+        <v>104425</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>

--- a/artfynd/A 26160-2024 artfynd.xlsx
+++ b/artfynd/A 26160-2024 artfynd.xlsx
@@ -3378,7 +3378,7 @@
         <v>69943578</v>
       </c>
       <c r="B24" t="n">
-        <v>104425</v>
+        <v>104435</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>

--- a/artfynd/A 26160-2024 artfynd.xlsx
+++ b/artfynd/A 26160-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY24"/>
+  <dimension ref="A1:AY27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3490,6 +3490,320 @@
         </is>
       </c>
     </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>133697864</v>
+      </c>
+      <c r="B25" t="n">
+        <v>106170</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>221141</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Gullviva</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Primula veris</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Kvarnen, Abbantorp, 185m SV, Öl</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>600780</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6292112</v>
+      </c>
+      <c r="S25" t="n">
+        <v>25</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Borgholm</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Öland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Högsrum</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF25" t="inlineStr"/>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Per Backman</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Per Backman, Karin Martinsson</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>133697852</v>
+      </c>
+      <c r="B26" t="n">
+        <v>103697</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>222002</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Underviol</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Viola mirabilis</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Kvarnen, Abbantorp, 185m SV, Öl</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>600780</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6292112</v>
+      </c>
+      <c r="S26" t="n">
+        <v>25</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Borgholm</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Öland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Högsrum</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF26" t="inlineStr"/>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Per Backman</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Per Backman, Karin Martinsson</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>133697890</v>
+      </c>
+      <c r="B27" t="n">
+        <v>99159</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>219864</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Sankt pers nycklar</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Orchis mascula</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Kvarnen, Abbantorp, 185m SV, Öl</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>600780</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6292112</v>
+      </c>
+      <c r="S27" t="n">
+        <v>25</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Borgholm</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Öland</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Högsrum</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF27" t="inlineStr"/>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Per Backman</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Per Backman, Karin Martinsson</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 26160-2024 artfynd.xlsx
+++ b/artfynd/A 26160-2024 artfynd.xlsx
@@ -3495,7 +3495,7 @@
         <v>133697864</v>
       </c>
       <c r="B25" t="n">
-        <v>106170</v>
+        <v>106172</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3601,7 +3601,7 @@
         <v>133697852</v>
       </c>
       <c r="B26" t="n">
-        <v>103697</v>
+        <v>103699</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3693,7 +3693,7 @@
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Per Backman, Karin Martinsson</t>
+          <t>Karin Martinsson, Per Backman</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
@@ -3703,7 +3703,7 @@
         <v>133697890</v>
       </c>
       <c r="B27" t="n">
-        <v>99159</v>
+        <v>99161</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>

--- a/artfynd/A 26160-2024 artfynd.xlsx
+++ b/artfynd/A 26160-2024 artfynd.xlsx
@@ -3495,7 +3495,7 @@
         <v>133697864</v>
       </c>
       <c r="B25" t="n">
-        <v>106172</v>
+        <v>106180</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3601,7 +3601,7 @@
         <v>133697852</v>
       </c>
       <c r="B26" t="n">
-        <v>103699</v>
+        <v>103707</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3693,7 +3693,7 @@
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Karin Martinsson, Per Backman</t>
+          <t>Per Backman, Karin Martinsson</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
@@ -3703,7 +3703,7 @@
         <v>133697890</v>
       </c>
       <c r="B27" t="n">
-        <v>99161</v>
+        <v>99169</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>

--- a/artfynd/A 26160-2024 artfynd.xlsx
+++ b/artfynd/A 26160-2024 artfynd.xlsx
@@ -3495,7 +3495,7 @@
         <v>133697864</v>
       </c>
       <c r="B25" t="n">
-        <v>106180</v>
+        <v>106208</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3601,7 +3601,7 @@
         <v>133697852</v>
       </c>
       <c r="B26" t="n">
-        <v>103707</v>
+        <v>103735</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3703,7 +3703,7 @@
         <v>133697890</v>
       </c>
       <c r="B27" t="n">
-        <v>99169</v>
+        <v>99197</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>

--- a/artfynd/A 26160-2024 artfynd.xlsx
+++ b/artfynd/A 26160-2024 artfynd.xlsx
@@ -3495,7 +3495,7 @@
         <v>133697864</v>
       </c>
       <c r="B25" t="n">
-        <v>106208</v>
+        <v>106218</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3601,7 +3601,7 @@
         <v>133697852</v>
       </c>
       <c r="B26" t="n">
-        <v>103735</v>
+        <v>103745</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3703,7 +3703,7 @@
         <v>133697890</v>
       </c>
       <c r="B27" t="n">
-        <v>99197</v>
+        <v>99207</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>

--- a/artfynd/A 26160-2024 artfynd.xlsx
+++ b/artfynd/A 26160-2024 artfynd.xlsx
@@ -3495,7 +3495,7 @@
         <v>133697864</v>
       </c>
       <c r="B25" t="n">
-        <v>106218</v>
+        <v>106219</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>

--- a/artfynd/A 26160-2024 artfynd.xlsx
+++ b/artfynd/A 26160-2024 artfynd.xlsx
@@ -3495,7 +3495,7 @@
         <v>133697864</v>
       </c>
       <c r="B25" t="n">
-        <v>106219</v>
+        <v>106221</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3601,7 +3601,7 @@
         <v>133697852</v>
       </c>
       <c r="B26" t="n">
-        <v>103745</v>
+        <v>103747</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3703,7 +3703,7 @@
         <v>133697890</v>
       </c>
       <c r="B27" t="n">
-        <v>99207</v>
+        <v>99209</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>

--- a/artfynd/A 26160-2024 artfynd.xlsx
+++ b/artfynd/A 26160-2024 artfynd.xlsx
@@ -3495,7 +3495,7 @@
         <v>133697864</v>
       </c>
       <c r="B25" t="n">
-        <v>106222</v>
+        <v>106229</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3601,7 +3601,7 @@
         <v>133697852</v>
       </c>
       <c r="B26" t="n">
-        <v>103748</v>
+        <v>103755</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3703,7 +3703,7 @@
         <v>133697890</v>
       </c>
       <c r="B27" t="n">
-        <v>99210</v>
+        <v>99217</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>

--- a/artfynd/A 26160-2024 artfynd.xlsx
+++ b/artfynd/A 26160-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY27"/>
+  <dimension ref="A1:AY46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>6245119</v>
+        <v>79855144</v>
       </c>
       <c r="B2" t="n">
-        <v>101691</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>100352</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,38 +686,49 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>224416</v>
+        <v>178</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ljus solvända</t>
+          <t>Skugglosta</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Helianthemum nummularium subsp. nummularium</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr"/>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>Bromopsis ramosa</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>(Huds.) Holub</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Abbantorp N, Öl</t>
+          <t>Abbantorp, Öl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>600970.6334626701</v>
+        <v>600839</v>
       </c>
       <c r="R2" t="n">
-        <v>6292145.152582166</v>
+        <v>6292088</v>
       </c>
       <c r="S2" t="n">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -746,22 +752,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2008-06-18</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2019-08-14</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2008-06-18</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2019-08-14</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Skogsbryn</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -770,81 +771,83 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
-      </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>Skogsbryn/ängsmark</t>
-        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Jan-Olof Petersson</t>
+          <t>Anders Waldenström</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Jan-Olof Petersson</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr"/>
+          <t>Anders Waldenström</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t>Inventering av Ölands kärlväxtflora.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>2711680</v>
+        <v>80855844</v>
       </c>
       <c r="B3" t="n">
-        <v>96361</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>100353</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>219865</v>
+        <v>178</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Johannesnycklar</t>
+          <t>Skugglosta</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Orchis militaris</t>
+          <t>Bromopsis ramosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>(Huds.) Holub</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Abbantorp N, Öl</t>
+          <t>Abbantorp, Öl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>600970.6334626701</v>
+        <v>600840</v>
       </c>
       <c r="R3" t="n">
-        <v>6292145.152582166</v>
+        <v>6292088</v>
       </c>
       <c r="S3" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -866,24 +869,19 @@
           <t>Högsrum</t>
         </is>
       </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>Hö-Bor-7701</t>
+        </is>
+      </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2008-06-18</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2019-08-14</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2008-06-18</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2019-08-14</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -892,85 +890,80 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>Skogsbryn/ängsmark</t>
-        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Jan-Olof Petersson</t>
+          <t>Thomas Gunnarsson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Jan-Olof Petersson</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr"/>
+          <t>Anders Waldenström</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>Inventering av Ölands kärlväxtflora., Floraväkteri Sverige</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>2758410</v>
+        <v>191093</v>
       </c>
       <c r="B4" t="n">
-        <v>107007</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106383</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220320</v>
+        <v>288</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ängsskära</t>
+          <t>Bredarun</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Serratula tinctoria</t>
+          <t>Centaurium erythraea</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Rafn</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Abbantorp N, Öl</t>
+          <t>Vedby S, Öl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>600970.6334626701</v>
+        <v>600820</v>
       </c>
       <c r="R4" t="n">
-        <v>6292145.152582166</v>
+        <v>6292193</v>
       </c>
       <c r="S4" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -994,22 +987,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2008-06-18</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2011-07-10</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2008-06-18</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2011-07-10</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1023,33 +1006,32 @@
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>Skogsbryn/ängsmark</t>
+          <t>åkervägkant</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Jan-Olof Petersson</t>
+          <t>Elna Hultqvist</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Jan-Olof Petersson</t>
-        </is>
-      </c>
-      <c r="AY4" t="inlineStr"/>
+          <t>Elna Hultqvist</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>Inventering av Ölands kärlväxtflora.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>5924343</v>
+        <v>192111</v>
       </c>
       <c r="B5" t="n">
-        <v>96251</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106383</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1057,42 +1039,37 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>223591</v>
+        <v>288</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Bredarun</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Centaurium erythraea</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
+          <t>Rafn</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Abbantorp N, Öl</t>
+          <t>Vedby by SV, Öl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>600970.6334626701</v>
+        <v>600627</v>
       </c>
       <c r="R5" t="n">
-        <v>6292145.152582166</v>
+        <v>6292397</v>
       </c>
       <c r="S5" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1116,22 +1093,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2008-06-18</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2011-07-27</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2008-06-18</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2011-07-27</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1145,67 +1112,80 @@
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>Skogsbryn/ängsmark</t>
+          <t>betat kärr</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Jan-Olof Petersson</t>
+          <t>Elna Hultqvist</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Jan-Olof Petersson</t>
-        </is>
-      </c>
-      <c r="AY5" t="inlineStr"/>
+          <t>Elna Hultqvist</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>Inventering av Ölands kärlväxtflora.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>6245413</v>
+        <v>73186140</v>
       </c>
       <c r="B6" t="n">
-        <v>101691</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79918</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>224416</v>
+        <v>1812</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ljus solvända</t>
+          <t>Staketflamlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Helianthemum nummularium subsp. nummularium</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr"/>
-      <c r="I6" t="inlineStr"/>
+          <t>Ramboldia insidiosa</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Th.Fr.) Hafellner</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Abbantorp N, söder om kvarn, Öl</t>
+          <t>Vedby Väderkvarn 10009, Öl</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>600829.7046162179</v>
+        <v>600869</v>
       </c>
       <c r="R6" t="n">
-        <v>6292179.588487921</v>
+        <v>6292270</v>
       </c>
       <c r="S6" t="n">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1229,27 +1209,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2008-07-12</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2018-09-15</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2008-07-12</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>NV</t>
+          <t>2018-09-15</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1258,43 +1223,48 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
-      <c r="AH6" t="inlineStr">
-        <is>
-          <t>Buskar</t>
-        </is>
-      </c>
-      <c r="AI6" t="inlineStr">
-        <is>
-          <t>fuktäng med hjulspår, obetad</t>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>gärdsgårdskantlav</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>Lecanora varia</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>Lecanora varia</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Elna Hultqvist</t>
+          <t>Robin Isaksson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Elna Hultqvist</t>
-        </is>
-      </c>
-      <c r="AY6" t="inlineStr"/>
+          <t>Robin Isaksson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>Lavfloran på Ölands väderkvarnar</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>2759423</v>
+        <v>66450948</v>
       </c>
       <c r="B7" t="n">
-        <v>107007</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>107611</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1302,16 +1272,16 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220320</v>
+        <v>1897</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ängsskära</t>
+          <t>Korskovall</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Serratula tinctoria</t>
+          <t>Melampyrum cristatum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1320,19 +1290,22 @@
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Abbantorp N, söder om kvarn, Öl</t>
+          <t>Vedby V, Öl</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>600857.1036608084</v>
+        <v>600481</v>
       </c>
       <c r="R7" t="n">
-        <v>6292136.93298418</v>
+        <v>6292600</v>
       </c>
       <c r="S7" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1356,27 +1329,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2008-07-12</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2017-06-28</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2008-07-12</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>NV</t>
+          <t>2017-06-28</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1388,14 +1346,9 @@
       <c r="AG7" t="b">
         <v>0</v>
       </c>
-      <c r="AH7" t="inlineStr">
-        <is>
-          <t>Buskar</t>
-        </is>
-      </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>fuktäng med hjulspår, obetad</t>
+          <t>fuktäng med torrare skogsbryn</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1406,49 +1359,48 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Elna Hultqvist</t>
-        </is>
-      </c>
-      <c r="AY7" t="inlineStr"/>
+          <t>Elna Hultqvist, Gert Hultqvist</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>Inventering av Ölands kärlväxtflora.</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>191093</v>
+        <v>879878</v>
       </c>
       <c r="B8" t="n">
-        <v>103397</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>104927</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>288</v>
+        <v>1939</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Bredarun</t>
+          <t>Kalkkrassing</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Centaurium erythraea</t>
+          <t>Erucastrum supinum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Rafn</t>
+          <t>(L.) Al-Shehbaz &amp; Warwick</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1462,13 +1414,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>600820.0534314569</v>
+        <v>600913</v>
       </c>
       <c r="R8" t="n">
-        <v>6292192.515097244</v>
+        <v>6292248</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1495,21 +1447,11 @@
           <t>2011-07-10</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2011-07-10</t>
         </is>
       </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
@@ -1521,7 +1463,7 @@
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>åkervägkant</t>
+          <t>leriga hjulspår över fuktäng</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1535,57 +1477,67 @@
           <t>Elna Hultqvist</t>
         </is>
       </c>
-      <c r="AY8" t="inlineStr"/>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>Inventering av Ölands kärlväxtflora.</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>192111</v>
+        <v>69943578</v>
       </c>
       <c r="B9" t="n">
-        <v>103397</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>104927</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>288</v>
+        <v>1939</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Bredarun</t>
+          <t>Kalkkrassing</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Centaurium erythraea</t>
+          <t>Erucastrum supinum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Rafn</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(L.) Al-Shehbaz &amp; Warwick</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Vedby by SV, Öl</t>
+          <t>Vedby söder om, Öl</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>600626.6857824081</v>
+        <v>600913</v>
       </c>
       <c r="R9" t="n">
-        <v>6292397.305030691</v>
+        <v>6292238</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1607,24 +1559,19 @@
           <t>Högsrum</t>
         </is>
       </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>Hö-Bor-3826</t>
+        </is>
+      </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2011-07-27</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2011-07-10</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2011-07-27</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2011-07-10</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1635,36 +1582,30 @@
       </c>
       <c r="AG9" t="b">
         <v>0</v>
-      </c>
-      <c r="AI9" t="inlineStr">
-        <is>
-          <t>betat kärr</t>
-        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Elna Hultqvist</t>
+          <t>Thomas Gunnarsson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Elna Hultqvist</t>
-        </is>
-      </c>
-      <c r="AY9" t="inlineStr"/>
+          <t>Thomas Gunnarsson, Ulla-Britt Andersson</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr">
+        <is>
+          <t>Inventering av Ölands kärlväxtflora., Floraväkteri Sverige</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>15670541</v>
+        <v>653177</v>
       </c>
       <c r="B10" t="n">
-        <v>5141</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101796</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1672,41 +1613,37 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100572</v>
+        <v>2076</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Mindre ekbock</t>
+          <t>Smalruta</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Cerambyx scopolii</t>
+          <t>Thalictrum simplex subsp. tenuifolium</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Fuessly, 1775</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+          <t>(Hartm.) Sterner</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Högsrum Abbantorp, Öl</t>
+          <t>Abbantorp, N om, Öl</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>600886.5906123527</v>
+        <v>600905</v>
       </c>
       <c r="R10" t="n">
-        <v>6292167.251576001</v>
+        <v>6292253</v>
       </c>
       <c r="S10" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1728,29 +1665,19 @@
           <t>Högsrum</t>
         </is>
       </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>Hö-Bor-1903</t>
+        </is>
+      </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>1995-07-29</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2008-07-12</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>1995-07-29</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Bengt Weidow coll</t>
+          <t>2008-07-12</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1762,21 +1689,25 @@
       <c r="AG10" t="b">
         <v>0</v>
       </c>
-      <c r="AR10" t="inlineStr"/>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>fuktäng med hjulspår, obetad</t>
+        </is>
+      </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Marit Persson</t>
+          <t>Öland- Floraväktarna</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Bengt Weidow</t>
+          <t>Elna Hultqvist</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>Långhorningsdatabasen (A. Lindhe)</t>
+          <t>Inventering av Ölands kärlväxtflora., Floraväkteri Sverige</t>
         </is>
       </c>
     </row>
@@ -1785,12 +1716,7 @@
         <v>15670539</v>
       </c>
       <c r="B11" t="n">
-        <v>5141</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>5207</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1822,10 +1748,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>600856.3775812164</v>
+        <v>600856</v>
       </c>
       <c r="R11" t="n">
-        <v>6292167.071897076</v>
+        <v>6292167</v>
       </c>
       <c r="S11" t="n">
         <v>50</v>
@@ -1855,19 +1781,9 @@
           <t>1999-06-20</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>1999-06-20</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
@@ -1904,56 +1820,52 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>66450867</v>
+        <v>15670541</v>
       </c>
       <c r="B12" t="n">
-        <v>96336</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>5207</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>219811</v>
+        <v>100572</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Brudsporre</t>
+          <t>Mindre ekbock</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Gymnadenia conopsea</t>
+          <t>Cerambyx scopolii</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
+          <t>Fuessly, 1775</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Vedby V, Öl</t>
+          <t>Högsrum Abbantorp, Öl</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>600480.6193513098</v>
+        <v>600887</v>
       </c>
       <c r="R12" t="n">
-        <v>6292600.486830491</v>
+        <v>6292167</v>
       </c>
       <c r="S12" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1977,22 +1889,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2017-06-28</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>1995-07-29</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2017-06-28</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>1995-07-29</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Bengt Weidow coll</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2004,35 +1911,30 @@
       <c r="AG12" t="b">
         <v>0</v>
       </c>
-      <c r="AI12" t="inlineStr">
-        <is>
-          <t>fuktäng med torrare skogsbryn</t>
-        </is>
-      </c>
+      <c r="AR12" t="inlineStr"/>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Elna Hultqvist</t>
+          <t>Marit Persson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Elna Hultqvist, Gert Hultqvist</t>
-        </is>
-      </c>
-      <c r="AY12" t="inlineStr"/>
+          <t>Bengt Weidow</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr">
+        <is>
+          <t>Långhorningsdatabasen (A. Lindhe)</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>66450556</v>
+        <v>98335855</v>
       </c>
       <c r="B13" t="n">
-        <v>96356</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>9406</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2040,40 +1942,51 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>219847</v>
+        <v>101246</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Ekoxe</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Lucanus cervus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Vedby V, Öl</t>
+          <t>6292168, 600966, Öl</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>600527.5018495156</v>
+        <v>600966</v>
       </c>
       <c r="R13" t="n">
-        <v>6292729.898055658</v>
+        <v>6292168</v>
       </c>
       <c r="S13" t="n">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2097,22 +2010,17 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2017-06-28</t>
-        </is>
-      </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-06-20</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2017-06-28</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-06-20</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Ekoxeuppropet 2020. död, överkörd</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2123,53 +2031,47 @@
       </c>
       <c r="AG13" t="b">
         <v>0</v>
-      </c>
-      <c r="AI13" t="inlineStr">
-        <is>
-          <t>äng med fuktängsstråk</t>
-        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Elna Hultqvist</t>
+          <t>Monika Sunhede</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Elna Hultqvist, Gert Hultqvist</t>
-        </is>
-      </c>
-      <c r="AY13" t="inlineStr"/>
+          <t>Via Monika Sunhede</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr">
+        <is>
+          <t>Ekoxeuppropet 2020</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>66450948</v>
+        <v>2159039</v>
       </c>
       <c r="B14" t="n">
-        <v>104493</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>111175</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1897</v>
+        <v>219677</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Korskovall</t>
+          <t>Murgröna</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Melampyrum cristatum</t>
+          <t>Hedera helix</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -2178,22 +2080,19 @@
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Vedby V, Öl</t>
+          <t>Vedby by S, Öl</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>600480.6193513098</v>
+        <v>600778</v>
       </c>
       <c r="R14" t="n">
-        <v>6292600.486830491</v>
+        <v>6292292</v>
       </c>
       <c r="S14" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2217,22 +2116,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2017-06-28</t>
-        </is>
-      </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2011-07-27</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2017-06-28</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2011-07-27</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2246,7 +2135,7 @@
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>fuktäng med torrare skogsbryn</t>
+          <t>betad blandskog</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2257,49 +2146,52 @@
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Elna Hultqvist, Gert Hultqvist</t>
-        </is>
-      </c>
-      <c r="AY14" t="inlineStr"/>
+          <t>Elna Hultqvist</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr">
+        <is>
+          <t>Inventering av Ölands kärlväxtflora.</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>66450928</v>
+        <v>66450682</v>
       </c>
       <c r="B15" t="n">
-        <v>96974</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99026</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>222322</v>
+        <v>219788</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ängsstarr</t>
+          <t>Ängsnycklar</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Carex hostiana</t>
+          <t>Dactylorhiza incarnata</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>DC.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2307,13 +2199,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>600480.6193513098</v>
+        <v>600528</v>
       </c>
       <c r="R15" t="n">
-        <v>6292600.486830491</v>
+        <v>6292730</v>
       </c>
       <c r="S15" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2340,19 +2232,14 @@
           <t>2017-06-28</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2017-06-28</t>
         </is>
       </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>00:00</t>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>flera</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2366,7 +2253,7 @@
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>fuktäng med torrare skogsbryn</t>
+          <t>äng med fuktängsstråk</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2377,22 +2264,21 @@
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Elna Hultqvist, Gert Hultqvist</t>
-        </is>
-      </c>
-      <c r="AY15" t="inlineStr"/>
+          <t>Gert Hultqvist, Elna Hultqvist</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr">
+        <is>
+          <t>Inventering av Ölands kärlväxtflora.</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>66450682</v>
+        <v>2929278</v>
       </c>
       <c r="B16" t="n">
-        <v>96242</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99096</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2400,44 +2286,37 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>219788</v>
+        <v>219798</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ängsnycklar</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Dactylorhiza incarnata</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Vedby V, Öl</t>
+          <t>Vedby by S, Öl</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>600527.5018495156</v>
+        <v>600778</v>
       </c>
       <c r="R16" t="n">
-        <v>6292729.898055658</v>
+        <v>6292292</v>
       </c>
       <c r="S16" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2461,27 +2340,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2017-06-28</t>
-        </is>
-      </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2011-07-27</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2017-06-28</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>flera</t>
+          <t>2011-07-27</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2495,7 +2359,7 @@
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>äng med fuktängsstråk</t>
+          <t>betad blandskog</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2506,60 +2370,56 @@
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Elna Hultqvist, Gert Hultqvist</t>
-        </is>
-      </c>
-      <c r="AY16" t="inlineStr"/>
+          <t>Elna Hultqvist</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr">
+        <is>
+          <t>Inventering av Ölands kärlväxtflora.</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>66450836</v>
+        <v>2297546</v>
       </c>
       <c r="B17" t="n">
-        <v>99590</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99120</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>221333</v>
+        <v>219811</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Backklöver</t>
+          <t>Brudsporre</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Trifolium montanum</t>
+          <t>Gymnadenia conopsea</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Vedby V, Öl</t>
+          <t>Vedby by SV, Öl</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>600524.9161133346</v>
+        <v>600650</v>
       </c>
       <c r="R17" t="n">
-        <v>6292631.703344095</v>
+        <v>6292482</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2586,22 +2446,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2017-06-28</t>
-        </is>
-      </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2011-07-27</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2017-06-28</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2011-07-27</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2615,7 +2465,7 @@
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>fuktäng med torrare skogsbryn</t>
+          <t>tuvig fuktäng med kärr</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -2626,22 +2476,21 @@
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Elna Hultqvist, Gert Hultqvist</t>
-        </is>
-      </c>
-      <c r="AY17" t="inlineStr"/>
+          <t>Elna Hultqvist</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr">
+        <is>
+          <t>Inventering av Ölands kärlväxtflora.</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>66450539</v>
+        <v>66450867</v>
       </c>
       <c r="B18" t="n">
-        <v>96252</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99120</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2649,21 +2498,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>223591</v>
+        <v>219811</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Brudsporre</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Gymnadenia conopsea</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2676,13 +2525,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>600527.5018495156</v>
+        <v>600481</v>
       </c>
       <c r="R18" t="n">
-        <v>6292729.898055658</v>
+        <v>6292600</v>
       </c>
       <c r="S18" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2709,21 +2558,11 @@
           <t>2017-06-28</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2017-06-28</t>
         </is>
       </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
@@ -2735,7 +2574,7 @@
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>äng med fuktängsstråk</t>
+          <t>fuktäng med torrare skogsbryn</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -2749,19 +2588,18 @@
           <t>Elna Hultqvist, Gert Hultqvist</t>
         </is>
       </c>
-      <c r="AY18" t="inlineStr"/>
+      <c r="AY18" t="inlineStr">
+        <is>
+          <t>Inventering av Ölands kärlväxtflora.</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>66450697</v>
+        <v>66450556</v>
       </c>
       <c r="B19" t="n">
-        <v>96370</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99142</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2769,21 +2607,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>219875</v>
+        <v>219847</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Grönvit nattviol</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Platanthera chlorantha</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Custer) Rchb.</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2796,10 +2634,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>600527.5018495156</v>
+        <v>600528</v>
       </c>
       <c r="R19" t="n">
-        <v>6292729.898055658</v>
+        <v>6292730</v>
       </c>
       <c r="S19" t="n">
         <v>50</v>
@@ -2829,19 +2667,9 @@
           <t>2017-06-28</t>
         </is>
       </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2017-06-28</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2869,19 +2697,18 @@
           <t>Elna Hultqvist, Gert Hultqvist</t>
         </is>
       </c>
-      <c r="AY19" t="inlineStr"/>
+      <c r="AY19" t="inlineStr">
+        <is>
+          <t>Inventering av Ölands kärlväxtflora.</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
         <v>66450969</v>
       </c>
       <c r="B20" t="n">
-        <v>96356</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99142</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2916,10 +2743,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>600480.6193513098</v>
+        <v>600481</v>
       </c>
       <c r="R20" t="n">
-        <v>6292600.486830491</v>
+        <v>6292600</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2949,19 +2776,9 @@
           <t>2017-06-28</t>
         </is>
       </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2017-06-28</t>
-        </is>
-      </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
@@ -2994,36 +2811,35 @@
           <t>Elna Hultqvist, Gert Hultqvist</t>
         </is>
       </c>
-      <c r="AY20" t="inlineStr"/>
+      <c r="AY20" t="inlineStr">
+        <is>
+          <t>Inventering av Ölands kärlväxtflora.</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>66450520</v>
+        <v>65297849</v>
       </c>
       <c r="B21" t="n">
-        <v>99590</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99147</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>221333</v>
+        <v>219864</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Backklöver</t>
+          <t>Sankt pers nycklar</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Trifolium montanum</t>
+          <t>Orchis mascula</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -3037,17 +2853,17 @@
       <c r="L21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Vedby V, Öl</t>
+          <t>Abbantorp, Öl</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>600527.5018495156</v>
+        <v>600962</v>
       </c>
       <c r="R21" t="n">
-        <v>6292729.898055658</v>
+        <v>6292105</v>
       </c>
       <c r="S21" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -3071,22 +2887,12 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2017-06-28</t>
-        </is>
-      </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2017-05-03</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2017-06-28</t>
-        </is>
-      </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2017-05-03</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3100,33 +2906,32 @@
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>äng med fuktängsstråk</t>
+          <t>vägkant</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Elna Hultqvist</t>
+          <t>Ulla-Britt Andersson</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Elna Hultqvist, Gert Hultqvist</t>
-        </is>
-      </c>
-      <c r="AY21" t="inlineStr"/>
+          <t>Ulla-Britt Andersson, Thomas Gunnarsson</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr">
+        <is>
+          <t>Inventering av Ölands kärlväxtflora.</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>66450635</v>
+        <v>133697890</v>
       </c>
       <c r="B22" t="n">
-        <v>103178</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99224</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3134,16 +2939,16 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>221141</v>
+        <v>219864</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Gullviva</t>
+          <t>Sankt pers nycklar</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Primula veris</t>
+          <t>Orchis mascula</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -3153,21 +2958,26 @@
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Vedby V, Öl</t>
+          <t>Kvarnen, Abbantorp, 185m SV, Öl</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>600527.5018495156</v>
+        <v>600780</v>
       </c>
       <c r="R22" t="n">
-        <v>6292729.898055658</v>
+        <v>6292112</v>
       </c>
       <c r="S22" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3191,22 +3001,12 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2017-06-28</t>
-        </is>
-      </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2017-06-28</t>
-        </is>
-      </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3215,38 +3015,29 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
+      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
-      </c>
-      <c r="AI22" t="inlineStr">
-        <is>
-          <t>äng med fuktängsstråk</t>
-        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Elna Hultqvist</t>
+          <t>Per Backman</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Elna Hultqvist, Gert Hultqvist</t>
+          <t>Per Backman, Karin Martinsson</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>66450871</v>
+        <v>2711680</v>
       </c>
       <c r="B23" t="n">
-        <v>96359</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99148</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3254,16 +3045,16 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>222118</v>
+        <v>219865</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Flugblomster</t>
+          <t>Johannesnycklar</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Ophrys insectifera</t>
+          <t>Orchis militaris</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -3271,35 +3062,25 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="K23" t="inlineStr">
         <is>
           <t>blomning</t>
         </is>
       </c>
-      <c r="L23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Vedby V, Öl</t>
+          <t>Abbantorp N, Öl</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>600480.6193513098</v>
+        <v>600971</v>
       </c>
       <c r="R23" t="n">
-        <v>6292600.486830491</v>
+        <v>6292145</v>
       </c>
       <c r="S23" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3323,27 +3104,12 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2017-06-28</t>
-        </is>
-      </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2008-06-18</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2017-06-28</t>
-        </is>
-      </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>klen</t>
+          <t>2008-06-18</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3357,28 +3123,32 @@
       </c>
       <c r="AI23" t="inlineStr">
         <is>
-          <t>fuktäng med torrare skogsbryn</t>
+          <t>Skogsbryn/ängsmark</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Elna Hultqvist</t>
+          <t>Jan-Olof Petersson</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Elna Hultqvist, Gert Hultqvist</t>
-        </is>
-      </c>
-      <c r="AY23" t="inlineStr"/>
+          <t>Jan-Olof Petersson</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr">
+        <is>
+          <t>Inventering av Ölands kärlväxtflora.</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>69943578</v>
+        <v>66450697</v>
       </c>
       <c r="B24" t="n">
-        <v>104435</v>
+        <v>99156</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3386,48 +3156,40 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1939</v>
+        <v>219875</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Kalkkrassing</t>
+          <t>Grönvit nattviol</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Erucastrum supinum</t>
+          <t>Platanthera chlorantha</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Al-Shehbaz &amp; Warwick</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Custer) Rchb.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
       <c r="L24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Vedby söder om, Öl</t>
+          <t>Vedby V, Öl</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>600913</v>
+        <v>600528</v>
       </c>
       <c r="R24" t="n">
-        <v>6292238</v>
+        <v>6292730</v>
       </c>
       <c r="S24" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3449,19 +3211,14 @@
           <t>Högsrum</t>
         </is>
       </c>
-      <c r="X24" t="inlineStr">
-        <is>
-          <t>Hö-Bor-3826</t>
-        </is>
-      </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2011-07-10</t>
+          <t>2017-06-28</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2011-07-10</t>
+          <t>2017-06-28</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3472,47 +3229,52 @@
       </c>
       <c r="AG24" t="b">
         <v>0</v>
+      </c>
+      <c r="AI24" t="inlineStr">
+        <is>
+          <t>äng med fuktängsstråk</t>
+        </is>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Thomas Gunnarsson</t>
+          <t>Elna Hultqvist</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Thomas Gunnarsson, Ulla-Britt Andersson</t>
+          <t>Elna Hultqvist, Gert Hultqvist</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr">
         <is>
-          <t>Inventering av Ölands kärlväxtflora., Floraväkteri Sverige</t>
+          <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>133697864</v>
+        <v>2758410</v>
       </c>
       <c r="B25" t="n">
-        <v>106229</v>
+        <v>110116</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>221141</v>
+        <v>220320</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Gullviva</t>
+          <t>Ängsskära</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Primula veris</t>
+          <t>Serratula tinctoria</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -3520,28 +3282,29 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L25" t="inlineStr"/>
-      <c r="N25" t="inlineStr"/>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Kvarnen, Abbantorp, 185m SV, Öl</t>
+          <t>Abbantorp N, Öl</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>600780</v>
+        <v>600971</v>
       </c>
       <c r="R25" t="n">
-        <v>6292112</v>
+        <v>6292145</v>
       </c>
       <c r="S25" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3565,12 +3328,12 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2008-06-18</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2008-06-18</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3579,46 +3342,54 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
-      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
+      </c>
+      <c r="AI25" t="inlineStr">
+        <is>
+          <t>Skogsbryn/ängsmark</t>
+        </is>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Per Backman</t>
+          <t>Jan-Olof Petersson</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Per Backman, Karin Martinsson</t>
-        </is>
-      </c>
-      <c r="AY25" t="inlineStr"/>
+          <t>Jan-Olof Petersson</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr">
+        <is>
+          <t>Inventering av Ölands kärlväxtflora.</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>133697852</v>
+        <v>2759423</v>
       </c>
       <c r="B26" t="n">
-        <v>103755</v>
+        <v>110116</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>222002</v>
+        <v>220320</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Underviol</t>
+          <t>Ängsskära</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Viola mirabilis</t>
+          <t>Serratula tinctoria</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -3627,23 +3398,19 @@
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
-      <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
-      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Kvarnen, Abbantorp, 185m SV, Öl</t>
+          <t>Abbantorp N, söder om kvarn, Öl</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>600780</v>
+        <v>600857</v>
       </c>
       <c r="R26" t="n">
-        <v>6292112</v>
+        <v>6292137</v>
       </c>
       <c r="S26" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3667,12 +3434,17 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2008-07-12</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2008-07-12</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>NV</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3681,46 +3453,59 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
-      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
+      </c>
+      <c r="AH26" t="inlineStr">
+        <is>
+          <t>Buskar</t>
+        </is>
+      </c>
+      <c r="AI26" t="inlineStr">
+        <is>
+          <t>fuktäng med hjulspår, obetad</t>
+        </is>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Per Backman</t>
+          <t>Elna Hultqvist</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Per Backman, Karin Martinsson</t>
-        </is>
-      </c>
-      <c r="AY26" t="inlineStr"/>
+          <t>Elna Hultqvist</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr">
+        <is>
+          <t>Inventering av Ölands kärlväxtflora.</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>133697890</v>
+        <v>65297870</v>
       </c>
       <c r="B27" t="n">
-        <v>99217</v>
+        <v>110116</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>219864</v>
+        <v>220320</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Sankt pers nycklar</t>
+          <t>Ängsskära</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Orchis mascula</t>
+          <t>Serratula tinctoria</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -3730,23 +3515,18 @@
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="J27" t="inlineStr"/>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+      <c r="K27" t="inlineStr"/>
       <c r="L27" t="inlineStr"/>
-      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Kvarnen, Abbantorp, 185m SV, Öl</t>
+          <t>Abbantorp, Öl</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>600780</v>
+        <v>600962</v>
       </c>
       <c r="R27" t="n">
-        <v>6292112</v>
+        <v>6292105</v>
       </c>
       <c r="S27" t="n">
         <v>25</v>
@@ -3773,12 +3553,12 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2017-05-03</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2017-05-03</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3787,22 +3567,2079 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
-      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
+      </c>
+      <c r="AI27" t="inlineStr">
+        <is>
+          <t>ohävdad torränsgrest</t>
+        </is>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
+          <t>Ulla-Britt Andersson</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Ulla-Britt Andersson, Thomas Gunnarsson</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr">
+        <is>
+          <t>Inventering av Ölands kärlväxtflora.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>133697872</v>
+      </c>
+      <c r="B28" t="n">
+        <v>104880</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>220460</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Tandrot</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Cardamine bulbifera</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr"/>
+      <c r="N28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Kvarnen, Abbantorp, 185m SV, Öl</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>600780</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6292112</v>
+      </c>
+      <c r="S28" t="n">
+        <v>25</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Borgholm</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Öland</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Högsrum</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF28" t="inlineStr"/>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
           <t>Per Backman</t>
         </is>
       </c>
-      <c r="AX27" t="inlineStr">
+      <c r="AX28" t="inlineStr">
         <is>
           <t>Per Backman, Karin Martinsson</t>
         </is>
       </c>
-      <c r="AY27" t="inlineStr"/>
+      <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>66450635</v>
+      </c>
+      <c r="B29" t="n">
+        <v>106155</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>221141</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Gullviva</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Primula veris</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Vedby V, Öl</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>600528</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6292730</v>
+      </c>
+      <c r="S29" t="n">
+        <v>50</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Borgholm</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Öland</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Högsrum</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2017-06-28</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2017-06-28</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI29" t="inlineStr">
+        <is>
+          <t>äng med fuktängsstråk</t>
+        </is>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Elna Hultqvist</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Elna Hultqvist, Gert Hultqvist</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr">
+        <is>
+          <t>Inventering av Ölands kärlväxtflora.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>133697864</v>
+      </c>
+      <c r="B30" t="n">
+        <v>106236</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>221141</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Gullviva</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Primula veris</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr"/>
+      <c r="N30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Kvarnen, Abbantorp, 185m SV, Öl</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>600780</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6292112</v>
+      </c>
+      <c r="S30" t="n">
+        <v>25</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Borgholm</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Öland</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Högsrum</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF30" t="inlineStr"/>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Per Backman</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Per Backman, Karin Martinsson</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>66450520</v>
+      </c>
+      <c r="B31" t="n">
+        <v>102442</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>221333</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Backklöver</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Trifolium montanum</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Vedby V, Öl</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>600528</v>
+      </c>
+      <c r="R31" t="n">
+        <v>6292730</v>
+      </c>
+      <c r="S31" t="n">
+        <v>50</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Borgholm</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Öland</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Högsrum</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2017-06-28</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2017-06-28</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI31" t="inlineStr">
+        <is>
+          <t>äng med fuktängsstråk</t>
+        </is>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Elna Hultqvist</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Elna Hultqvist, Gert Hultqvist</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr">
+        <is>
+          <t>Inventering av Ölands kärlväxtflora.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>66450836</v>
+      </c>
+      <c r="B32" t="n">
+        <v>102442</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>221333</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Backklöver</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Trifolium montanum</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Vedby V, Öl</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>600525</v>
+      </c>
+      <c r="R32" t="n">
+        <v>6292632</v>
+      </c>
+      <c r="S32" t="n">
+        <v>10</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Borgholm</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Öland</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Högsrum</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2017-06-28</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2017-06-28</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI32" t="inlineStr">
+        <is>
+          <t>fuktäng med torrare skogsbryn</t>
+        </is>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Elna Hultqvist</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Elna Hultqvist, Gert Hultqvist</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr">
+        <is>
+          <t>Inventering av Ölands kärlväxtflora.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>54815601</v>
+      </c>
+      <c r="B33" t="n">
+        <v>107624</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>221735</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Åkerrödtoppa</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Odontites vernus</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(Bellardi) Dumort.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Abbantorp, västra byn, Öl</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>601003</v>
+      </c>
+      <c r="R33" t="n">
+        <v>6292104</v>
+      </c>
+      <c r="S33" t="n">
+        <v>5</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Borgholm</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Öland</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Högsrum</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2015-08-12</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2015-08-12</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI33" t="inlineStr">
+        <is>
+          <t>vid åkerväg</t>
+        </is>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Elna Hultqvist</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Elna Hultqvist</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr">
+        <is>
+          <t>Inventering av Ölands kärlväxtflora.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>133697675</v>
+      </c>
+      <c r="B34" t="n">
+        <v>104197</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>221987</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Skogsbingel</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Mercurialis perennis</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
+      <c r="N34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Kvarnen, Abbantorp, 200m S, Öl</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>600856</v>
+      </c>
+      <c r="R34" t="n">
+        <v>6292077</v>
+      </c>
+      <c r="S34" t="n">
+        <v>25</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Borgholm</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Öland</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Högsrum</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF34" t="inlineStr"/>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Per Backman</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Per Backman, Karin Martinsson</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>133697843</v>
+      </c>
+      <c r="B35" t="n">
+        <v>104197</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>221987</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Skogsbingel</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Mercurialis perennis</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
+      <c r="N35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Kvarnen, Abbantorp, 185m SV, Öl</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>600780</v>
+      </c>
+      <c r="R35" t="n">
+        <v>6292112</v>
+      </c>
+      <c r="S35" t="n">
+        <v>25</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Borgholm</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Öland</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Högsrum</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF35" t="inlineStr"/>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Per Backman</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Per Backman, Karin Martinsson</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>133697852</v>
+      </c>
+      <c r="B36" t="n">
+        <v>103762</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>222002</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Underviol</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Viola mirabilis</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
+      <c r="N36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Kvarnen, Abbantorp, 185m SV, Öl</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>600780</v>
+      </c>
+      <c r="R36" t="n">
+        <v>6292112</v>
+      </c>
+      <c r="S36" t="n">
+        <v>25</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Borgholm</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Öland</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Högsrum</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF36" t="inlineStr"/>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Per Backman</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Per Backman, Karin Martinsson</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>66450871</v>
+      </c>
+      <c r="B37" t="n">
+        <v>99145</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>222118</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Flugblomster</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Ophrys insectifera</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Vedby V, Öl</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>600481</v>
+      </c>
+      <c r="R37" t="n">
+        <v>6292600</v>
+      </c>
+      <c r="S37" t="n">
+        <v>25</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Borgholm</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Öland</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Högsrum</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2017-06-28</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2017-06-28</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>klen</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI37" t="inlineStr">
+        <is>
+          <t>fuktäng med torrare skogsbryn</t>
+        </is>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Elna Hultqvist</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Elna Hultqvist, Gert Hultqvist</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr">
+        <is>
+          <t>Inventering av Ölands kärlväxtflora.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>4823083</v>
+      </c>
+      <c r="B38" t="n">
+        <v>99802</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>222322</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Ängsstarr</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Carex hostiana</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>DC.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Vedby by SV, Öl</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>600650</v>
+      </c>
+      <c r="R38" t="n">
+        <v>6292482</v>
+      </c>
+      <c r="S38" t="n">
+        <v>10</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Borgholm</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Öland</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Högsrum</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2011-07-27</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2011-07-27</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI38" t="inlineStr">
+        <is>
+          <t>tuvig fuktäng med kärr</t>
+        </is>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Elna Hultqvist</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Elna Hultqvist</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr">
+        <is>
+          <t>Inventering av Ölands kärlväxtflora.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>66450928</v>
+      </c>
+      <c r="B39" t="n">
+        <v>99802</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>222322</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Ängsstarr</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Carex hostiana</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>DC.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Vedby V, Öl</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>600481</v>
+      </c>
+      <c r="R39" t="n">
+        <v>6292600</v>
+      </c>
+      <c r="S39" t="n">
+        <v>25</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Borgholm</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Öland</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Högsrum</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2017-06-28</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2017-06-28</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI39" t="inlineStr">
+        <is>
+          <t>fuktäng med torrare skogsbryn</t>
+        </is>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Elna Hultqvist</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Elna Hultqvist, Gert Hultqvist</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr">
+        <is>
+          <t>Inventering av Ölands kärlväxtflora.</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>133697883</v>
+      </c>
+      <c r="B40" t="n">
+        <v>100806</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>222584</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Bergsslok</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Melica nutans</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr"/>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr"/>
+      <c r="N40" t="inlineStr"/>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Kvarnen, Abbantorp, 185m SV, Öl</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>600780</v>
+      </c>
+      <c r="R40" t="n">
+        <v>6292112</v>
+      </c>
+      <c r="S40" t="n">
+        <v>25</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Borgholm</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Öland</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Högsrum</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF40" t="inlineStr"/>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Per Backman</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Per Backman, Karin Martinsson</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>133697671</v>
+      </c>
+      <c r="B41" t="n">
+        <v>101325</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>222783</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Gulsippa</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Anemone ranunculoides</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr"/>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr"/>
+      <c r="N41" t="inlineStr"/>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Kvarnen, Abbantorp, 200m S, Öl</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>600856</v>
+      </c>
+      <c r="R41" t="n">
+        <v>6292077</v>
+      </c>
+      <c r="S41" t="n">
+        <v>25</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Borgholm</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Öland</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Högsrum</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF41" t="inlineStr"/>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Per Backman</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Per Backman, Karin Martinsson</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>5791393</v>
+      </c>
+      <c r="B42" t="n">
+        <v>103407</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>223248</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Lundalm</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Ulmus minor</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>Mill.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Vedby S, Öl</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>600913</v>
+      </c>
+      <c r="R42" t="n">
+        <v>6292248</v>
+      </c>
+      <c r="S42" t="n">
+        <v>25</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Borgholm</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Öland</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Högsrum</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2011-07-10</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2011-07-10</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI42" t="inlineStr">
+        <is>
+          <t>landsvägskant</t>
+        </is>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Elna Hultqvist</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Elna Hultqvist</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr">
+        <is>
+          <t>Inventering av Ölands kärlväxtflora.</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>5924343</v>
+      </c>
+      <c r="B43" t="n">
+        <v>99036</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>223591</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Skogsnycklar</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>(Druce) Hyl.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Abbantorp N, Öl</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>600971</v>
+      </c>
+      <c r="R43" t="n">
+        <v>6292145</v>
+      </c>
+      <c r="S43" t="n">
+        <v>50</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Borgholm</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Öland</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Högsrum</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2008-06-18</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2008-06-18</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI43" t="inlineStr">
+        <is>
+          <t>Skogsbryn/ängsmark</t>
+        </is>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Jan-Olof Petersson</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Jan-Olof Petersson</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr">
+        <is>
+          <t>Inventering av Ölands kärlväxtflora.</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>66450539</v>
+      </c>
+      <c r="B44" t="n">
+        <v>99036</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>223591</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Skogsnycklar</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>(Druce) Hyl.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="J44" t="inlineStr"/>
+      <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr"/>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Vedby V, Öl</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>600528</v>
+      </c>
+      <c r="R44" t="n">
+        <v>6292730</v>
+      </c>
+      <c r="S44" t="n">
+        <v>50</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Borgholm</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Öland</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Högsrum</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2017-06-28</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2017-06-28</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI44" t="inlineStr">
+        <is>
+          <t>äng med fuktängsstråk</t>
+        </is>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Elna Hultqvist</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>Elna Hultqvist, Gert Hultqvist</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr">
+        <is>
+          <t>Inventering av Ölands kärlväxtflora.</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>6245119</v>
+      </c>
+      <c r="B45" t="n">
+        <v>104640</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>224416</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Ljus solvända</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Helianthemum nummularium subsp. nummularium</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr"/>
+      <c r="I45" t="inlineStr"/>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Abbantorp N, Öl</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>600971</v>
+      </c>
+      <c r="R45" t="n">
+        <v>6292145</v>
+      </c>
+      <c r="S45" t="n">
+        <v>50</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Borgholm</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Öland</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Högsrum</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2008-06-18</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2008-06-18</t>
+        </is>
+      </c>
+      <c r="AD45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI45" t="inlineStr">
+        <is>
+          <t>Skogsbryn/ängsmark</t>
+        </is>
+      </c>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>Jan-Olof Petersson</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>Jan-Olof Petersson</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr">
+        <is>
+          <t>Inventering av Ölands kärlväxtflora.</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>6245413</v>
+      </c>
+      <c r="B46" t="n">
+        <v>104640</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>224416</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Ljus solvända</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Helianthemum nummularium subsp. nummularium</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr"/>
+      <c r="I46" t="inlineStr"/>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>Abbantorp N, söder om kvarn, Öl</t>
+        </is>
+      </c>
+      <c r="Q46" t="n">
+        <v>600830</v>
+      </c>
+      <c r="R46" t="n">
+        <v>6292180</v>
+      </c>
+      <c r="S46" t="n">
+        <v>50</v>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>Borgholm</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Öland</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Högsrum</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>2008-07-12</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>2008-07-12</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>NV</t>
+        </is>
+      </c>
+      <c r="AD46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH46" t="inlineStr">
+        <is>
+          <t>Buskar</t>
+        </is>
+      </c>
+      <c r="AI46" t="inlineStr">
+        <is>
+          <t>fuktäng med hjulspår, obetad</t>
+        </is>
+      </c>
+      <c r="AT46" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>Elna Hultqvist</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>Elna Hultqvist</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr">
+        <is>
+          <t>Inventering av Ölands kärlväxtflora.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 26160-2024 artfynd.xlsx
+++ b/artfynd/A 26160-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY46"/>
+  <dimension ref="A1:AY47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5424,49 +5424,48 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>6245119</v>
+        <v>135208352</v>
       </c>
       <c r="B45" t="n">
-        <v>104640</v>
+        <v>99113</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>224416</v>
+        <v>223591</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Ljus solvända</t>
+          <t>Skogsnycklar</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Helianthemum nummularium subsp. nummularium</t>
-        </is>
-      </c>
-      <c r="H45" t="inlineStr"/>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>(Druce) Hyl.</t>
+        </is>
+      </c>
       <c r="I45" t="inlineStr"/>
-      <c r="K45" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Abbantorp N, Öl</t>
+          <t>Vägområde, Öl</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>600971</v>
+        <v>600439</v>
       </c>
       <c r="R45" t="n">
-        <v>6292145</v>
+        <v>6292762</v>
       </c>
       <c r="S45" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5490,12 +5489,17 @@
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>2008-06-18</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2008-06-18</t>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>1 ex i blom 50 cm från beläggningskanten</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5506,32 +5510,27 @@
       </c>
       <c r="AG45" t="b">
         <v>0</v>
-      </c>
-      <c r="AI45" t="inlineStr">
-        <is>
-          <t>Skogsbryn/ängsmark</t>
-        </is>
       </c>
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Jan-Olof Petersson</t>
+          <t>Edvin Åhman</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Jan-Olof Petersson</t>
+          <t>Edvin Åhman, Christine Sandberg</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr">
         <is>
-          <t>Inventering av Ölands kärlväxtflora.</t>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>6245413</v>
+        <v>6245119</v>
       </c>
       <c r="B46" t="n">
         <v>104640</v>
@@ -5556,16 +5555,21 @@
       </c>
       <c r="H46" t="inlineStr"/>
       <c r="I46" t="inlineStr"/>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Abbantorp N, söder om kvarn, Öl</t>
+          <t>Abbantorp N, Öl</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>600830</v>
+        <v>600971</v>
       </c>
       <c r="R46" t="n">
-        <v>6292180</v>
+        <v>6292145</v>
       </c>
       <c r="S46" t="n">
         <v>50</v>
@@ -5592,17 +5596,12 @@
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>2008-07-12</t>
+          <t>2008-06-18</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2008-07-12</t>
-        </is>
-      </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>NV</t>
+          <t>2008-06-18</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5614,28 +5613,135 @@
       <c r="AG46" t="b">
         <v>0</v>
       </c>
-      <c r="AH46" t="inlineStr">
-        <is>
-          <t>Buskar</t>
-        </is>
-      </c>
       <c r="AI46" t="inlineStr">
         <is>
-          <t>fuktäng med hjulspår, obetad</t>
+          <t>Skogsbryn/ängsmark</t>
         </is>
       </c>
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
+          <t>Jan-Olof Petersson</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>Jan-Olof Petersson</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr">
+        <is>
+          <t>Inventering av Ölands kärlväxtflora.</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>6245413</v>
+      </c>
+      <c r="B47" t="n">
+        <v>104640</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>224416</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Ljus solvända</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Helianthemum nummularium subsp. nummularium</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr"/>
+      <c r="I47" t="inlineStr"/>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>Abbantorp N, söder om kvarn, Öl</t>
+        </is>
+      </c>
+      <c r="Q47" t="n">
+        <v>600830</v>
+      </c>
+      <c r="R47" t="n">
+        <v>6292180</v>
+      </c>
+      <c r="S47" t="n">
+        <v>50</v>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>Borgholm</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Öland</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Högsrum</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>2008-07-12</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>2008-07-12</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>NV</t>
+        </is>
+      </c>
+      <c r="AD47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH47" t="inlineStr">
+        <is>
+          <t>Buskar</t>
+        </is>
+      </c>
+      <c r="AI47" t="inlineStr">
+        <is>
+          <t>fuktäng med hjulspår, obetad</t>
+        </is>
+      </c>
+      <c r="AT47" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
           <t>Elna Hultqvist</t>
         </is>
       </c>
-      <c r="AX46" t="inlineStr">
+      <c r="AX47" t="inlineStr">
         <is>
           <t>Elna Hultqvist</t>
         </is>
       </c>
-      <c r="AY46" t="inlineStr">
+      <c r="AY47" t="inlineStr">
         <is>
           <t>Inventering av Ölands kärlväxtflora.</t>
         </is>

--- a/artfynd/A 26160-2024 artfynd.xlsx
+++ b/artfynd/A 26160-2024 artfynd.xlsx
@@ -5519,7 +5519,7 @@
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Edvin Åhman, Christine Sandberg</t>
+          <t>Christine Sandberg, Edvin Åhman</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr">

--- a/artfynd/A 26160-2024 artfynd.xlsx
+++ b/artfynd/A 26160-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY47"/>
+  <dimension ref="A1:AY48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5519,7 +5519,7 @@
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Christine Sandberg, Edvin Åhman</t>
+          <t>Edvin Åhman, Christine Sandberg</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr">
@@ -5744,6 +5744,114 @@
       <c r="AY47" t="inlineStr">
         <is>
           <t>Inventering av Ölands kärlväxtflora.</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>135447142</v>
+      </c>
+      <c r="B48" t="n">
+        <v>104720</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>224416</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Ljus solvända</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Helianthemum nummularium subsp. nummularium</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr"/>
+      <c r="I48" t="inlineStr"/>
+      <c r="J48" t="inlineStr"/>
+      <c r="K48" t="inlineStr"/>
+      <c r="L48" t="inlineStr"/>
+      <c r="N48" t="inlineStr"/>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>Väg 967, fyndplats 003, Öl</t>
+        </is>
+      </c>
+      <c r="Q48" t="n">
+        <v>600496</v>
+      </c>
+      <c r="R48" t="n">
+        <v>6292791</v>
+      </c>
+      <c r="S48" t="n">
+        <v>6</v>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>Borgholm</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>Öland</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>Högsrum</t>
+        </is>
+      </c>
+      <c r="X48" t="inlineStr"/>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>Rikligt hela väg</t>
+        </is>
+      </c>
+      <c r="AD48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF48" t="inlineStr"/>
+      <c r="AG48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT48" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>Edvin Åhman</t>
+        </is>
+      </c>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>Edvin Åhman, Christine Sandberg</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr">
+        <is>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
         </is>
       </c>
     </row>

--- a/artfynd/A 26160-2024 artfynd.xlsx
+++ b/artfynd/A 26160-2024 artfynd.xlsx
@@ -5519,7 +5519,7 @@
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Christine Sandberg, Edvin Åhman</t>
+          <t>Edvin Åhman, Christine Sandberg</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr">

--- a/artfynd/A 26160-2024 artfynd.xlsx
+++ b/artfynd/A 26160-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY48"/>
+  <dimension ref="A1:AZ48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -791,6 +796,11 @@
           <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79855144</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -910,6 +920,11 @@
           <t>Inventering av Ölands kärlväxtflora., Floraväkteri Sverige</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80855844</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1025,6 +1040,11 @@
           <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/191093</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1131,6 +1151,11 @@
           <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/192111</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1256,6 +1281,11 @@
       <c r="AY6" t="inlineStr">
         <is>
           <t>Lavfloran på Ölands väderkvarnar</t>
+        </is>
+      </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73186140</t>
         </is>
       </c>
     </row>
@@ -1367,6 +1397,11 @@
           <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/66450948</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1482,6 +1517,11 @@
           <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/879878</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1599,6 +1639,11 @@
           <t>Inventering av Ölands kärlväxtflora., Floraväkteri Sverige</t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69943578</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1710,6 +1755,11 @@
           <t>Inventering av Ölands kärlväxtflora., Floraväkteri Sverige</t>
         </is>
       </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/653177</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1817,6 +1867,11 @@
           <t>Långhorningsdatabasen (A. Lindhe)</t>
         </is>
       </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/15670539</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1928,6 +1983,11 @@
           <t>Långhorningsdatabasen (A. Lindhe)</t>
         </is>
       </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/15670541</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2048,6 +2108,11 @@
           <t>Ekoxeuppropet 2020</t>
         </is>
       </c>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98335855</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2154,6 +2219,11 @@
           <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/2159039</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2272,6 +2342,11 @@
           <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/66450682</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2378,6 +2453,11 @@
           <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/2929278</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2482,6 +2562,11 @@
       <c r="AY17" t="inlineStr">
         <is>
           <t>Inventering av Ölands kärlväxtflora.</t>
+        </is>
+      </c>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/2297546</t>
         </is>
       </c>
     </row>
@@ -2593,6 +2678,11 @@
           <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/66450867</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2702,6 +2792,11 @@
           <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/66450556</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2816,6 +2911,11 @@
           <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/66450969</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2925,6 +3025,11 @@
           <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/65297849</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -3031,6 +3136,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133697890</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3140,6 +3250,11 @@
       <c r="AY23" t="inlineStr">
         <is>
           <t>Inventering av Ölands kärlväxtflora.</t>
+        </is>
+      </c>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/2711680</t>
         </is>
       </c>
     </row>
@@ -3251,6 +3366,11 @@
           <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/66450697</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3366,6 +3486,11 @@
           <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/2758410</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3480,6 +3605,11 @@
       <c r="AY26" t="inlineStr">
         <is>
           <t>Inventering av Ölands kärlväxtflora.</t>
+        </is>
+      </c>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/2759423</t>
         </is>
       </c>
     </row>
@@ -3591,6 +3721,11 @@
           <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/65297870</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3697,6 +3832,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133697872</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3806,6 +3946,11 @@
           <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/66450635</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3912,6 +4057,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133697864</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -4021,6 +4171,11 @@
           <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/66450520</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -4130,6 +4285,11 @@
           <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/66450836</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4234,6 +4394,11 @@
       <c r="AY33" t="inlineStr">
         <is>
           <t>Inventering av Ölands kärlväxtflora.</t>
+        </is>
+      </c>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/54815601</t>
         </is>
       </c>
     </row>
@@ -4338,6 +4503,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133697675</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4440,6 +4610,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133697843</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4542,6 +4717,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133697852</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4668,6 +4848,11 @@
           <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/66450871</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4772,6 +4957,11 @@
       <c r="AY38" t="inlineStr">
         <is>
           <t>Inventering av Ölands kärlväxtflora.</t>
+        </is>
+      </c>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/4823083</t>
         </is>
       </c>
     </row>
@@ -4883,6 +5073,11 @@
           <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/66450928</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4989,6 +5184,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133697883</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -5095,6 +5295,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133697671</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -5201,6 +5406,11 @@
           <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/5791393</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5310,6 +5520,11 @@
       <c r="AY43" t="inlineStr">
         <is>
           <t>Inventering av Ölands kärlväxtflora.</t>
+        </is>
+      </c>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/5924343</t>
         </is>
       </c>
     </row>
@@ -5421,6 +5636,11 @@
           <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/66450539</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5527,6 +5747,11 @@
           <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
         </is>
       </c>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135208352</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5634,6 +5859,11 @@
           <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/6245119</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5744,6 +5974,11 @@
       <c r="AY47" t="inlineStr">
         <is>
           <t>Inventering av Ölands kärlväxtflora.</t>
+        </is>
+      </c>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/6245413</t>
         </is>
       </c>
     </row>
@@ -5854,8 +6089,62 @@
           <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
         </is>
       </c>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135447142</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/A 26160-2024 artfynd.xlsx
+++ b/artfynd/A 26160-2024 artfynd.xlsx
@@ -5739,7 +5739,7 @@
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Edvin Åhman, Christine Sandberg</t>
+          <t>Christine Sandberg, Edvin Åhman</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr">

--- a/artfynd/A 26160-2024 artfynd.xlsx
+++ b/artfynd/A 26160-2024 artfynd.xlsx
@@ -5739,7 +5739,7 @@
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Christine Sandberg, Edvin Åhman</t>
+          <t>Edvin Åhman, Christine Sandberg</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr">

--- a/artfynd/A 26160-2024 artfynd.xlsx
+++ b/artfynd/A 26160-2024 artfynd.xlsx
@@ -5647,7 +5647,7 @@
         <v>135208352</v>
       </c>
       <c r="B45" t="n">
-        <v>99113</v>
+        <v>99160</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5987,7 +5987,7 @@
         <v>135447142</v>
       </c>
       <c r="B48" t="n">
-        <v>104720</v>
+        <v>104774</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>

--- a/artfynd/A 26160-2024 artfynd.xlsx
+++ b/artfynd/A 26160-2024 artfynd.xlsx
@@ -5647,7 +5647,7 @@
         <v>135208352</v>
       </c>
       <c r="B45" t="n">
-        <v>99160</v>
+        <v>99187</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5739,7 +5739,7 @@
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Edvin Åhman, Christine Sandberg</t>
+          <t>Christine Sandberg, Edvin Åhman</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr">
@@ -5987,7 +5987,7 @@
         <v>135447142</v>
       </c>
       <c r="B48" t="n">
-        <v>104774</v>
+        <v>104801</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>

--- a/artfynd/A 26160-2024 artfynd.xlsx
+++ b/artfynd/A 26160-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ46"/>
+  <dimension ref="A1:AZ48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5644,49 +5644,48 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>6245119</v>
+        <v>135208352</v>
       </c>
       <c r="B45" t="n">
-        <v>104640</v>
+        <v>99192</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>224416</v>
+        <v>223591</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Ljus solvända</t>
+          <t>Skogsnycklar</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Helianthemum nummularium subsp. nummularium</t>
-        </is>
-      </c>
-      <c r="H45" t="inlineStr"/>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>(Druce) Hyl.</t>
+        </is>
+      </c>
       <c r="I45" t="inlineStr"/>
-      <c r="K45" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Abbantorp N, Öl</t>
+          <t>Vägområde, Öl</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>600971</v>
+        <v>600439</v>
       </c>
       <c r="R45" t="n">
-        <v>6292145</v>
+        <v>6292762</v>
       </c>
       <c r="S45" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5710,12 +5709,17 @@
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>2008-06-18</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2008-06-18</t>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>1 ex i blom 50 cm från beläggningskanten</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5726,37 +5730,32 @@
       </c>
       <c r="AG45" t="b">
         <v>0</v>
-      </c>
-      <c r="AI45" t="inlineStr">
-        <is>
-          <t>Skogsbryn/ängsmark</t>
-        </is>
       </c>
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Jan-Olof Petersson</t>
+          <t>Edvin Åhman</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Jan-Olof Petersson</t>
+          <t>Edvin Åhman, Christine Sandberg</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr">
         <is>
-          <t>Inventering av Ölands kärlväxtflora.</t>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
         </is>
       </c>
       <c r="AZ45" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/6245119</t>
+          <t>https://artportalen.se/Sighting/135208352</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>6245413</v>
+        <v>6245119</v>
       </c>
       <c r="B46" t="n">
         <v>104640</v>
@@ -5781,16 +5780,21 @@
       </c>
       <c r="H46" t="inlineStr"/>
       <c r="I46" t="inlineStr"/>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Abbantorp N, söder om kvarn, Öl</t>
+          <t>Abbantorp N, Öl</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>600830</v>
+        <v>600971</v>
       </c>
       <c r="R46" t="n">
-        <v>6292180</v>
+        <v>6292145</v>
       </c>
       <c r="S46" t="n">
         <v>50</v>
@@ -5817,17 +5821,12 @@
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>2008-07-12</t>
+          <t>2008-06-18</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2008-07-12</t>
-        </is>
-      </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>NV</t>
+          <t>2008-06-18</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5839,35 +5838,260 @@
       <c r="AG46" t="b">
         <v>0</v>
       </c>
-      <c r="AH46" t="inlineStr">
-        <is>
-          <t>Buskar</t>
-        </is>
-      </c>
       <c r="AI46" t="inlineStr">
         <is>
-          <t>fuktäng med hjulspår, obetad</t>
+          <t>Skogsbryn/ängsmark</t>
         </is>
       </c>
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
+          <t>Jan-Olof Petersson</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>Jan-Olof Petersson</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr">
+        <is>
+          <t>Inventering av Ölands kärlväxtflora.</t>
+        </is>
+      </c>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/6245119</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>6245413</v>
+      </c>
+      <c r="B47" t="n">
+        <v>104640</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>224416</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Ljus solvända</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Helianthemum nummularium subsp. nummularium</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr"/>
+      <c r="I47" t="inlineStr"/>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>Abbantorp N, söder om kvarn, Öl</t>
+        </is>
+      </c>
+      <c r="Q47" t="n">
+        <v>600830</v>
+      </c>
+      <c r="R47" t="n">
+        <v>6292180</v>
+      </c>
+      <c r="S47" t="n">
+        <v>50</v>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>Borgholm</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Öland</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Högsrum</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>2008-07-12</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>2008-07-12</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>NV</t>
+        </is>
+      </c>
+      <c r="AD47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH47" t="inlineStr">
+        <is>
+          <t>Buskar</t>
+        </is>
+      </c>
+      <c r="AI47" t="inlineStr">
+        <is>
+          <t>fuktäng med hjulspår, obetad</t>
+        </is>
+      </c>
+      <c r="AT47" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
           <t>Elna Hultqvist</t>
         </is>
       </c>
-      <c r="AX46" t="inlineStr">
+      <c r="AX47" t="inlineStr">
         <is>
           <t>Elna Hultqvist</t>
         </is>
       </c>
-      <c r="AY46" t="inlineStr">
+      <c r="AY47" t="inlineStr">
         <is>
           <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
-      <c r="AZ46" t="inlineStr">
+      <c r="AZ47" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/6245413</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>135447142</v>
+      </c>
+      <c r="B48" t="n">
+        <v>104806</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>224416</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Ljus solvända</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Helianthemum nummularium subsp. nummularium</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr"/>
+      <c r="I48" t="inlineStr"/>
+      <c r="J48" t="inlineStr"/>
+      <c r="K48" t="inlineStr"/>
+      <c r="L48" t="inlineStr"/>
+      <c r="N48" t="inlineStr"/>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>Väg 967, fyndplats 003, Öl</t>
+        </is>
+      </c>
+      <c r="Q48" t="n">
+        <v>600496</v>
+      </c>
+      <c r="R48" t="n">
+        <v>6292791</v>
+      </c>
+      <c r="S48" t="n">
+        <v>6</v>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>Borgholm</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>Öland</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>Högsrum</t>
+        </is>
+      </c>
+      <c r="X48" t="inlineStr"/>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>Rikligt hela väg</t>
+        </is>
+      </c>
+      <c r="AD48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF48" t="inlineStr"/>
+      <c r="AG48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT48" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>Edvin Åhman</t>
+        </is>
+      </c>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>Edvin Åhman, Christine Sandberg</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr">
+        <is>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+        </is>
+      </c>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135447142</t>
         </is>
       </c>
     </row>
@@ -5918,6 +6142,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 26160-2024 artfynd.xlsx
+++ b/artfynd/A 26160-2024 artfynd.xlsx
@@ -5647,7 +5647,7 @@
         <v>135208352</v>
       </c>
       <c r="B45" t="n">
-        <v>99192</v>
+        <v>99194</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5987,7 +5987,7 @@
         <v>135447142</v>
       </c>
       <c r="B48" t="n">
-        <v>104806</v>
+        <v>104808</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>

--- a/artfynd/A 26160-2024 artfynd.xlsx
+++ b/artfynd/A 26160-2024 artfynd.xlsx
@@ -5987,7 +5987,7 @@
         <v>135447142</v>
       </c>
       <c r="B48" t="n">
-        <v>104808</v>
+        <v>104828</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
